--- a/Phase6.2/quantized (Cleaned)/load_28.xlsx
+++ b/Phase6.2/quantized (Cleaned)/load_28.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8720"/>
+    <workbookView windowWidth="18350" windowHeight="8720"/>
   </bookViews>
   <sheets>
     <sheet name="Timestamp logs" sheetId="1" r:id="rId1"/>
@@ -34,14 +34,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -497,28 +490,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -527,118 +523,115 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -703,6 +696,9381 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Sensing Unit Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$A$1:$A$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>29.0181</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.7828</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21.0807</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>27.65</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15.6103</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>23.7729</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>23.1001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>24.8438</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>23.5881</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>21.7527</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>36.0242</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>24.1026</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>21.9953</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>28.755</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>21.1705</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>22.0953</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>22.7276</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>19.2932</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>16.959</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>23.1903</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>18.6813</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>27.5569</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>19.1603</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>23.8407</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>23.4506</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>24.519</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>21.2209</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>39.9727</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>21.729</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>19.301</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>27.4731</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>145.4786</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>36.9816</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>22.062</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>24.6402</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>26.9491</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>29.4399</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>27.3986</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>25.4928</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>23.6982</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>16.1672</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>19.1686</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>17.661</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>26.0451</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>20.7699</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>19.1987</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>20.4423</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>32.3804</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>23.8967</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>44.7357</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>18.3819</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>22.686</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>39.3671</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>17.5837</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>20.7099</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>40.9624</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>35.2335</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>31.0133</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>35.0699</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>30.2264</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>19.5187</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>35.2564</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>34.3824</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>19.9548</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>25.4724</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>12.2316</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>18.9108</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>23.1292</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>11.4299</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>13.0075</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>12.6891</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>18.5469</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>14.5878</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>9.8399</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>13.3526</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>12.2284</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>14.7859</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>18.2649</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>10.7107</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>14.3628</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>11.8065</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>10.549</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>11.9754</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>20.2399</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>11.3869</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>15.9649</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>18.1629</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>19.6378</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>17.3704</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>12.8935</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>20.8102</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>12.7475</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>14.1895</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>11.8423</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>11.0619</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>11.7132</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>10.6433</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>16.8241</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>14.7893</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>26.7184</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>18.9238</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>16.2068</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>10.3077</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>18.0763</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>10.0586</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>18.2044</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>21.5745</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>17.716</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>10.2987</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>18.7249</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>15.8851</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>11.7116</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>11.0997</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>18.5513</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>25.2343</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>12.0274</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>15.2566</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>22.0389</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>10.9966</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>11.0926</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>22.8819</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>16.9266</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>13.9501</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>15.4046</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>10.8006</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>21.7599</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>12.6237</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>10.585</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>13.793</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>10.2613</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>19.0262</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>10.5981</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>10.2421</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>25.2869</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>21.6955</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>13.1903</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>15.5807</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>34.6172</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>12.2585</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>31.4778</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>13.7453</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>18.4099</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>11.4785</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>19.4744</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>17.1971</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>11.4201</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>11.0936</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>17.8194</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>11.8209</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>13.606</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>14.6837</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>18.7191</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>20.0213</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>20.9483</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>21.2584</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>23.9353</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>28.3766</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>15.91</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>17.3096</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>23.3954</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>11.218</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>13.4319</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>10.5612</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>11.547</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>25.417</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>17.2088</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>15.4699</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>13.4893</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>12.4503</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>16.5504</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>15.6397</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>18.8798</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>112.2805</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>11.2487</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>10.9109</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>21.1298</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>11.0013</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>10.8683</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>11.0457</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>10.9788</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>11.2908</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>11.5329</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>11.6651</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>20.7415</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>16.2239</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>14.0468</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>16.1937</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>12.9469</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>30.4013</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>22.9919</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>11.3176</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>12.6017</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>19.0896</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>11.0549</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>21.8948</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>13.9545</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>13.3538</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>21.8381</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>10.3281</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>24.1462</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>10.1281</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>11.0234</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>28.3316</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>18.4104</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>10.2448</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>15.9913</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>13.7852</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>10.8496</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>15.693</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>18.1597</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>19.0197</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>11.7152</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>12.8305</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>18.6951</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>26.3697</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>13.8566</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>25.4374</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>16.6836</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>10.4742</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>24.8463</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>12.0733</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>10.8301</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>10.7484</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>11.8784</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>25.0037</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>20.5237</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>20.0792</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>12.6076</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>10.8481</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>12.2332</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>18.7688</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>14.0956</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>13.2542</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>19.6508</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>12.7759</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>10.8718</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>11.0312</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>20.2393</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>16.8552</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>12.5993</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>17.6014</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>12.3297</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>10.3759</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>15.7019</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>13.7309</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>12.7972</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>22.7723</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>14.8174</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>15.1389</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>11.0163</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>16.1058</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>11.1715</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>12.1804</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>15.9007</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>19.6177</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>12.5706</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>10.5542</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>21.1185</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>12.9291</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>15.9339</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>13.402</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>16.0352</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>14.0707</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>10.2702</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>9.5192</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>14.1268</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>18.8443</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>16.9801</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>11.9096</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>12.2134</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>11.9639</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>20.6974</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>20.0959</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>21.5561</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>12.9546</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>23.4269</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>16.0372</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>17.9639</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>14.7962</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>15.9124</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>10.9371</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>12.4728</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>15.1142</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>14.8476</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>12.6794</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>14.7297</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>10.6038</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>13.8919</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>11.6211</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>20.2718</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>13.6211</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>11.7515</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>27.3125</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>19.5536</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>22.1718</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>15.2969</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>20.8677</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>11.2062</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>22.5109</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>20.9587</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>12.3924</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>10.2934</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>16.9638</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>11.8558</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>11.5029</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>21.5544</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>14.6217</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>16.4596</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>13.0872</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>11.6142</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>15.4454</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>14.1804</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>27.2816</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>10.3764</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>14.2188</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>22.4786</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>18.5122</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>13.4065</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>15.4776</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>10.8283</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>12.9938</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>24.5672</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>17.8353</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>27.1587</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>18.9526</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>14.4832</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>10.9556</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>20.4172</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>17.3096</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>17.3548</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>13.4254</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>14.0721</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>12.6338</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>12.8099</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>20.1441</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>21.0845</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>12.8105</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>11.1693</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>20.8932</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>13.3516</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>14.8279</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>23.5669</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>16.959</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>12.6437</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>14.7067</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>12.5155</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>11.2653</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>13.2719</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>11.1995</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>12.7856</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>27.3765</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>11.6186</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>21.7337</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>11.2313</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>16.755</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>20.483</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>11.7195</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>10.4772</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>10.6062</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>28.3624</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>11.7495</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>19.2132</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>14.5283</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>15.0249</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>11.0436</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>21.7937</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>16.6572</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>15.8358</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>23.6702</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>13.0304</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>10.9445</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>17.0957</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>16.5176</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>13.4751</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>79.4696</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>32.4027</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>21.3846</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>10.5705</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>10.3492</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>19.4944</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>11.6047</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>20.4024</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>19.3216</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>14.6315</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>13.1373</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>10.8121</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>19.9384</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>20.1087</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>24.9162</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>21.5731</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>10.8997</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>14.3278</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>17.9848</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>11.3117</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>29.2593</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>20.5777</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>13.845</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>9.2262</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>11.0678</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>17.3153</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>11.0719</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>12.2044</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>10.9403</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>15.2234</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>15.8338</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>14.8853</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>12.7124</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>17.7931</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>12.1049</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>11.2913</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>12.5195</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>13.0653</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>11.5223</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>21.538</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>10.4782</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>15.8834</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>13.7239</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>20.1408</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>11.3118</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>10.2689</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>19.773</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>13.1146</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>16.1284</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>19.0774</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>13.9898</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>21.1817</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>15.2128</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>14.2368</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>10.4267</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>9.4403</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>9.1305</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>16.9321</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>17.6633</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>12.3564</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>14.4572</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>11.3263</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>16.9766</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>21.0053</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>10.964</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>12.596</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>10.9212</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>11.8059</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>12.3731</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>10.7042</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>14.6335</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>25.5012</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>14.6925</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>12.8434</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>17.1141</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>10.9409</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>33.6496</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>10.8034</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>10.908</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>17.3739</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>12.1626</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>10.8689</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>11.3273</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>18.0605</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>12.2693</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>10.7282</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>21.3345</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>18.6856</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>31.0932</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>11.3025</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>25.177</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>11.9923</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>11.475</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>13.4534</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>15.8573</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>11.1728</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>22.8922</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>20.3241</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>22.0003</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>10.0218</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>12.4829</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>21.7456</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>11.8043</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>12.0909</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>18.4035</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>13.5544</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>22.041</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>11.5314</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>13.9485</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>25.7785</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>10.5764</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>11.2421</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>10.8799</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>12.9111</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>9.776</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>19.6413</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>19.1894</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>10.5155</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>22.1555</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>12.4284</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>19.7429</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>10.8349</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>13.2476</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="463111265"/>
+        <c:axId val="727703073"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="463111265"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="727703073"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="727703073"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="463111265"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Queue Lifetime: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$B$1:$B$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>664.90391</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>656.873042</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>861.380755</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1280.106785</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1312.249308</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1876.173206</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1796.224927</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1772.357195</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2535.139019</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2666.530073</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3066.280538</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3099.402959</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3221.343898</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3635.198095</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>3663.513229</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3883.249197</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3906.749812</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4077.827277</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>4318.835551</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>4539.632208</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4972.548245</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5008.057674</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4973.067843</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5292.330688</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>5293.642185</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5565.415316</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5567.744314</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5471.321275</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5527.601931</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>5561.447265</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>5608.384412</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>5794.876109</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>5687.823146</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5515.645373</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>5607.868939</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>5713.862215</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>5841.176909</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>5836.428947</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>5765.954549</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>5830.416747</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>6004.374754</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6115.979031</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>6353.275271</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>6287.030619</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>6349.066242</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>6514.755123</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>6488.37391</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>6496.45717</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>6694.359061</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>6382.994246</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>6568.43117</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>6796.834112</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>6912.559244</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>6874.673196</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>6523.11824</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>6708.136701</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>6789.837151</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>6494.035852</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>6840.585006</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>6391.294233</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>6271.77967</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>6543.965034</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>6584.023427</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>6687.395559</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>6405.533011</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>6682.426552</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>6247.598329</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>6142.380195</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>6276.051852</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>6030.614557</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>6214.40316</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>6346.925269</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>6147.02589</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>6122.037979</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>5949.869365</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>6223.425896</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>5716.001042</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>5721.826005</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>6022.446221</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>6116.454935</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>5962.677355</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>6074.710292</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>5834.597006</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>6057.752034</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>6164.771608</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>5806.524413</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5495.436202</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>5441.229765</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>5712.169425</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5169.555622</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>5487.945568</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5403.890103</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5320.015422</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5128.007878</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>4967.140976</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5124.41833</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>4808.599398</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5216.167116</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>5372.629916</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>4930.580711</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>4896.42693</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5178.021488</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5013.715382</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>4509.559205</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>4553.234201</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>4466.591263</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>4444.460278</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>4371.646404</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>4368.464341</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>4284.282169</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>4376.406046</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>4699.405931</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>4527.758943</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>4542.748466</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>4290.943703</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>4476.48677</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>4267.681135</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>4676.653893</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>4519.40733</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>4375.765875</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>4604.663403</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4254.034339</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>4478.023289</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>4303.398505</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>4326.217745</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>4342.37593</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>4371.442439</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>4425.612859</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>4329.289955</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>4377.572628</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>4188.901231</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>4322.851866</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>4288.002225</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>4400.503522</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>4417.736672</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>4307.267495</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>4396.982003</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>4524.375449</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>4473.753973</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>4336.748095</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>4507.898841</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>4243.008451</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>4276.561119</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>4299.987526</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>4263.339297</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>4380.931155</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>4244.320164</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>4236.380756</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>4163.72684</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>4174.914046</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>3933.136165</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>4082.67658</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>4140.296732</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>4073.089941</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>4017.328573</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>3825.550629</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>3888.171592</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>3927.815551</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>3983.40648</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>3792.283582</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>3720.15084</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>3717.375698</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>3678.168447</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>3719.077015</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>3546.038268</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>3695.183817</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>3719.153281</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>3677.030556</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>3547.123506</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>3551.647237</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>3378.633486</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>3456.973105</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>3766.720597</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>3741.684088</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>3577.777843</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3641.153093</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>3481.547948</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>3746.336784</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>3859.904233</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>3921.979959</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>3822.875376</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>3712.813612</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>3741.513387</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>3775.464149</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>3729.604473</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>3517.342243</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>3681.752153</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>3770.232979</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>3722.135548</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>3483.200213</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>3707.602883</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>3821.812006</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>3769.256108</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>3518.937702</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>3640.45965</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>3600.017111</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>3567.181614</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>3578.214558</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>3561.865066</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>3641.436661</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>3615.415952</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>3232.055456</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>3542.646928</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>3361.946023</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>3509.927431</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>3590.173454</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>3562.160883</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>3757.960578</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>3641.887256</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>3590.665169</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>3537.605532</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>3680.613607</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>3733.655742</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>3621.98528</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>3844.742742</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>3727.663504</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>3784.169327</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>3721.795803</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>4077.854446</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>4020.304745</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>4063.191476</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>3951.2178</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>3882.588459</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>4103.746096</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>4021.571542</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>4038.980017</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>3701.224383</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>3962.333743</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>3979.770147</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>3850.875761</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>3771.086698</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>3824.884532</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>3955.05906</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>3846.702566</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>4078.295183</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>3884.47509</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>3979.840066</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>3985.615638</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>3655.227088</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>3631.995854</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>3644.420187</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>3877.839387</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>3926.600534</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>3792.644117</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>3575.666888</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>3545.417701</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>3989.603885</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>3598.290599</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>3581.46311</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>3577.721863</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>3933.094668</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>3814.04339</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>3563.701712</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>3635.906758</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>4087.13804</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>3720.313861</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>3725.110757</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>3709.166592</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>3880.393713</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>4096.009233</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>3914.161403</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>4048.560271</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>4160.074941</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>4544.609164</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>4478.813857</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>4399.829562</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>4086.887282</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>4364.146711</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>4580.880903</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>4748.44189</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>4315.936613</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>4442.547341</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>4482.851602</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>4837.507272</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>4660.940171</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>4705.015488</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>4662.094681</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>4748.00234</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>4362.091366</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>4471.886118</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>4872.114596</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>4818.44336</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>4322.585687</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>4672.172791</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>4617.574243</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>4445.870523</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>4353.523827</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>4177.695395</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>4169.69325</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>4185.568673</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>4359.855286</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>4014.274428</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>4106.090036</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>4216.83536</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>4245.065859</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>4128.076601</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>4233.5872</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>3972.035704</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>4015.747777</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>4024.921528</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>3944.58986</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>4210.82225</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>4290.192644</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>4516.904061</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>4141.554724</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>4235.245485</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>4262.233101</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>4335.137593</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>4375.911422</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>4350.186245</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>4367.030858</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>4498.273297</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>4566.46896</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>4623.397843</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>4374.739357</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>4486.287861</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>4436.528675</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>4462.151917</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>4582.131294</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>4555.485266</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>4781.714422</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>4641.795529</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>4559.004943</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>4661.097042</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>4749.17084</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>4361.644193</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>4375.332525</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>4396.335866</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>4297.90772</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>4138.096794</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>4337.629652</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>4118.366167</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>4199.785819</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>4249.30928</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>4304.8862</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>3933.227217</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>4033.111558</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>4112.226809</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>4046.794666</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>4126.156359</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>3977.307036</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>3638.820318</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>3673.932367</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>3789.789653</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>3705.253799</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>3641.6726</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>3886.537815</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>3711.531843</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>3551.442265</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>3613.33349</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>3814.038377</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>3634.430023</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>3637.924573</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>3743.098002</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>3715.384518</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>3485.897299</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>3636.435628</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>3683.45692</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>3548.565623</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>3892.950481</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>3625.423277</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>3487.169871</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>3916.547336</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>3643.876917</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>3676.66284</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>3607.316572</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>3893.702963</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>3790.698486</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>3785.431489</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>3938.099634</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>4118.368021</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>4023.837903</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>4049.745646</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>4085.573165</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>3867.036583</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>3988.850535</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>3996.968303</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>3949.435518</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>4066.30198</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>3989.942637</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>3918.394639</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>3894.097678</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>3999.469233</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>3770.166972</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>3931.361177</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>3947.580828</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>3923.870313</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>3915.211208</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>4092.516154</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>4024.106213</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>3879.733873</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>4005.357301</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>4260.285603</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>4204.233438</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>3635.430554</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>3757.291527</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>4120.545286</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>4136.613986</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>3850.269311</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>3768.259035</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>4085.969523</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>3963.864127</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>3923.693726</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>4136.272563</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>4099.101334</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>4055.729813</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>4158.425422</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>4024.335916</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>3878.90927</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>3968.854165</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>4080.103447</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>4123.66405</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>3946.064082</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>4299.308719</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>4169.060672</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>4067.646582</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>3784.282756</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>3882.394894</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>3818.967857</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>4321.892179</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>3831.310271</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>3858.262602</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>3838.112796</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>4236.45619</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>3939.049924</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>3951.360166</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>4366.876908</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>4223.526487</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>4139.136628</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>4162.35233</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>4173.086323</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>4203.281535</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>4153.6116</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>4246.486355</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>4161.567198</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>4177.220407</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>4257.268911</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>3867.54429</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>4209.896188</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>4312.049659</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>4170.979772</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>4258.162249</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>4361.627387</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>4201.949542</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>4044.067046</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>4125.333259</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>4315.141029</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>4146.847917</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>4082.974074</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>4205.760745</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>3682.854847</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>4152.233285</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>4065.452144</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>4084.252991</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>3820.655165</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>3959.636495</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>4025.000191</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>4043.40517</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>3766.10088</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>3727.840449</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>3657.488392</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>4082.269798</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>3670.581726</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>3568.578486</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>3612.197694</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>3952.251894</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>3883.065121</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>3655.273543</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>3707.767873</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>4012.421171</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>3960.829032</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>3593.534987</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>3511.1507</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>3970.540222</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>4093.986815</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>3650.936933</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>3755.611574</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>3738.252188</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>4149.550115</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>4269.705341</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>4253.438502</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>4250.671313</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>4384.992902</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>4459.649223</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>4979.661974</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>4669.486429</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>4551.760217</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>4709.747581</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>5155.387598</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>4732.59036</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>4721.466843</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>4865.984308</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>5291.114373</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>5155.785374</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>5063.141901</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>5555.5283</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>5735.905463</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="847401412"/>
+        <c:axId val="561171548"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="847401412"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="561171548"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="561171548"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="847401412"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="0" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Inference Program: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$C$1:$C$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>698.660201</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1273.104979</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>504.302632</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>595.343715</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>506.749933</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>903.691475</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>799.33121</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1297.227246</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>809.193214</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>502.701193</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>708.192339</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>594.472339</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>788.226359</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>296.823883</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>489.035713</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>504.15668</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>698.440532</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1011.416543</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>698.771735</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>493.634312</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>395.325313</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>773.252283</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>791.072714</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>398.429179</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>19634.775316</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>698.669514</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1196.418469</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>501.802913</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1009.229958</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>902.808012</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>797.922179</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>696.842462</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1096.02561</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>1099.105248</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>695.276546</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>896.532844</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>498.163812</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>900.520289</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>700.345256</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>993.672324</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1073.865645</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>696.186868</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1098.945591</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>902.083675</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>698.065634</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>705.753246</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>552.577261</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>903.585909</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>647.906452</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1199.125902</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>791.849062</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>699.699157</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>801.857476</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>893.123058</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>802.804325</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>976.408246</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>694.056278</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>597.550279</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>606.952506</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>898.485379</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1022.596193</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>598.445879</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>800.859004</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>578.905569</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>603.717246</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>898.352722</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>1097.403302</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>396.360928</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>700.898317</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>701.72878</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>698.805098</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>400.477892</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>795.903001</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>695.538071</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>607.418518</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>504.786491</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>1400.52197</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>1104.836217</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>692.476235</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>505.227974</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>991.721523</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>889.951297</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>300.822569</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>393.89748</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>303.903972</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>497.909033</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>446.866251</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>690.590128</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>704.620104</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>345.123989</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>500.691973</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>498.526466</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>497.047402</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>395.982826</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>1094.060024</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>847.05274</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>499.919769</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>396.605424</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>697.628606</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>950.692162</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>304.35608</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>399.051724</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>900.712636</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>499.220961</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>848.527127</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>598.318428</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>604.190697</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>907.693226</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>699.742931</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>854.118354</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>595.27339</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>598.555903</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>978.480575</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>392.205455</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>794.238912</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>598.712595</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>802.041114</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>806.878236</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>996.421421</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>498.377584</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>404.229173</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>701.740149</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>719.46796</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>995.295305</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>799.300472</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>701.261016</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>496.459388</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>696.449776</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>907.855517</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>503.822577</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>799.87709</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>1147.452851</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>601.522196</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>911.335445</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>504.976254</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>514.339345</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>596.489464</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>750.658841</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>580.783812</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>504.966656</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>518.374555</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>889.497364</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>600.016591</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>795.330392</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>499.743796</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>494.215593</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>494.28877</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>903.482477</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>999.387095</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>502.998244</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>604.988315</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>394.246233</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>695.827383</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>799.675806</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>293.154465</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>598.674526</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>601.417637</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>595.015662</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>500.087761</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>509.089596</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>324.314528</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>701.246664</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>596.379927</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>684.403185</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>513.842477</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>503.573337</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>419.647071</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>589.516834</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>1051.320661</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1080.292865</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>594.445863</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>485.701307</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>402.607722</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>805.450145</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1044.613037</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>499.815453</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>773.237544</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>595.690723</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>404.970985</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>501.598454</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>504.387935</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>395.059338</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>697.9421</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>404.287856</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>592.049831</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>397.711071</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>795.169234</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>701.551175</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>505.552617</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>597.526652</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>396.432679</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>347.026293</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>776.78362</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>800.572987</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>397.408607</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>944.766156</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>595.732563</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>495.957918</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>799.506619</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>396.868006</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>647.948361</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>905.707499</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>596.440308</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>1100.899395</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>651.978451</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>396.922206</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>399.131628</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>449.338816</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>497.051538</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>502.188272</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>1067.674494</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>750.681269</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>799.790103</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>596.200201</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>504.688729</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>644.707251</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>927.639178</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>906.227785</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>401.294133</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>845.753662</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>596.417207</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>571.044448</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>591.718199</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>410.510765</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>602.278632</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>701.123701</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>679.835512</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>703.007005</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>600.545223</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>823.701763</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>423.886612</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>743.400639</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>522.52164</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>396.931573</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>673.452684</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>495.776887</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>378.042012</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>1003.39467</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>396.226546</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>916.462492</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>725.966034</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>507.216224</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>743.850059</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>496.766114</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>595.44675</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>599.125842</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>430.227807</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>603.060735</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>597.722396</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>698.722528</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>827.800093</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>647.125903</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>604.029115</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>598.037455</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>604.770513</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>893.967716</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>1033.9256</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>700.496897</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>696.86214</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>1013.979337</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>1196.805428</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>777.627163</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>603.122006</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>1076.679985</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>595.912524</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>697.123863</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>853.056603</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>799.78098</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>501.590903</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>696.985361</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>1099.143755</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>592.158751</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>776.806153</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>602.72485</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>501.714882</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>882.575628</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>401.144187</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>690.02298</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>599.216716</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>996.958147</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>598.82542</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>595.559195</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>706.774435</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>1050.909237</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>592.304533</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>529.871729</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>589.42141</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>792.391972</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>402.463121</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>998.591148</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>696.395469</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>800.002779</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>671.961327</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>396.046611</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>502.441859</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>646.069792</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>500.552212</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>800.66306</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>899.144859</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>1207.838766</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>927.594722</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>798.348115</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>399.117503</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>803.300521</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>877.633673</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>855.346915</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>598.839971</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>896.516216</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>697.210173</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>920.947379</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>790.885715</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>501.552918</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>602.029435</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>800.986467</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>1044.961423</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>751.43083</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>873.179006</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>619.353042</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>405.154685</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>909.964</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>406.79977</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>600.138795</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>695.714349</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>702.302219</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>541.16357</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>497.729664</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>584.459807</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>699.180844</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>594.56989</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>723.620067</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>802.217924</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>498.064436</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>752.570041</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>804.583405</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>802.442009</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>504.512745</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>544.455813</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>531.957082</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>491.820012</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>497.947556</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>545.257596</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>799.370841</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>406.789126</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>695.718421</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>606.579131</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>460.815231</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>599.081207</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>826.375409</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>592.531983</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>543.781206</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>497.417202</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>700.36163</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>452.586752</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>795.669896</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>498.038004</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>895.755698</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>701.48906</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>601.871542</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>871.037842</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>645.099248</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>607.443339</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>399.546103</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>651.596925</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>603.362108</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>647.184022</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>785.174467</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>986.007263</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>892.712887</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>695.325687</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>699.174818</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>706.847075</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>400.21958</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>718.046899</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>415.192468</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>598.341802</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>496.109384</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>595.234966</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>467.379149</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>606.844462</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>697.708099</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>726.314578</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>712.060273</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>792.983765</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>691.996644</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>734.105545</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>632.262995</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>595.798286</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>700.967262</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>804.206365</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>895.563392</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>599.865564</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>575.39855</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>803.356779</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>600.114554</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>649.790717</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>504.4288</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>748.292471</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>544.467023</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>502.103833</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>799.918554</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>596.158717</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>504.881565</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>801.133726</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>627.869826</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>500.774917</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>607.136114</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>1258.331546</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>694.540277</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>702.950443</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>687.058249</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>694.740016</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>729.376224</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>606.16012</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>441.09897</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>305.63367</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>879.379674</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>599.425501</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>653.303423</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>601.334037</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>603.106027</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>697.220396</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>1301.438162</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>613.559654</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>702.511653</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>685.377332</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>698.240643</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>701.251926</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>494.883122</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>801.534207</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>552.342845</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>700.522617</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>897.403816</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>693.762829</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>698.293791</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>898.44165</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>606.19964</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>605.071939</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>793.017217</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>489.359203</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>518.870245</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>548.208498</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>505.795097</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>502.594452</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>700.752782</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>892.108228</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>562.376875</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>503.747529</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>706.151858</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>947.252911</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>504.922058</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>600.629691</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>503.620192</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>397.883426</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>680.05117</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>649.354907</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>499.361298</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>523.398709</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>724.265543</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>647.119872</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>646.352382</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>595.689729</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>706.707759</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>598.642343</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>605.507001</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>603.105179</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>549.129267</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>546.328443</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>595.17422</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>505.778886</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>852.397039</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>551.953527</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>972.969905</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>800.288252</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>455.740436</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>850.961096</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>1201.825639</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>1096.540702</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>848.1446</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>995.298157</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>594.868584</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>1292.159279</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>1199.860308</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>800.88614</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>895.899715</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>799.565933</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>803.201484</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>704.53855</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>849.915648</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>993.487259</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>698.956608</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>899.395345</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>1251.881294</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>954.374076</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>970.965165</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>795.982675</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>1095.469212</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>850.735696</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="910405863"/>
+        <c:axId val="235234486"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="910405863"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="235234486"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="235234486"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="910405863"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="2500"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr defTabSz="914400">
+              <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="75000"/>
+                    <a:lumOff val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t>Entire Pipeline: latency (ms) vs test number</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="0" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>'Timestamp logs'!$D$1:$D$497</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="497"/>
+                <c:pt idx="0">
+                  <c:v>1392.582211</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1950.760821</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1386.764087</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1903.1005</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1834.609541</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2803.637581</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2618.656237</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>3094.428241</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3367.920333</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>3190.983966</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3810.497077</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3717.977898</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4031.565557</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>3960.776978</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4173.719442</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>4409.501177</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>4627.917944</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5108.53702</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5034.566286</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5056.45682</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>5386.554858</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>5808.866857</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5783.300857</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>5714.600567</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>24951.868101</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6288.60383</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6785.383683</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6013.096888</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6558.560889</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6483.556277</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6433.779691</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>6637.197171</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6820.830356</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6636.812621</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6327.785685</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>6637.344159</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>6368.780621</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>6764.347836</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>6491.792605</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>6847.787271</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>7094.407599</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>6831.334499</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>7469.881862</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>7215.159394</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>7067.901776</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>7239.707069</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>7061.393471</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>7432.423479</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>7366.162213</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>7626.855848</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>7378.662132</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>7519.219269</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>7753.78382</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>7785.379954</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>7346.632465</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>7725.507347</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>7519.126929</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>7122.599431</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7482.607412</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>7320.006012</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>7313.894563</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>7177.667313</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>7419.264831</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>7286.255928</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>7034.722657</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>7593.010874</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>7363.912431</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>6561.870323</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>6988.380069</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>6745.350837</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>6925.897358</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>6765.950061</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>6957.516691</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>6827.41595</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>6570.640483</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>6740.440787</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>7131.308912</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>6844.927122</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>6725.633156</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>6636.045709</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>6966.205378</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>6975.210589</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>6147.394975</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>6471.889414</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>6480.06248</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>6320.398346</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>5960.465353</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>6151.457693</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>6434.159929</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>5527.573111</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>6009.447741</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>5915.164069</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>5831.252324</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>5535.833004</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>6072.2629</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>5983.18427</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>5319.162467</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>5629.59664</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>6085.047822</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>5907.991273</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>5219.70681</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>5593.280012</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>5924.735718</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>5026.856466</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>5411.819928</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>5083.114091</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>5070.225475</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>5297.05563</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>5078.505972</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>5157.125423</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>4987.564536</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>5309.673434</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>5517.339218</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>4953.505221</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>5110.416915</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>5087.226765</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>5084.978849</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>5505.571029</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>5526.825351</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>4885.236059</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>5031.774476</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4972.701088</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>5211.441349</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>5314.09841</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>5136.318817</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>5065.396846</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>4880.525527</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>5132.647635</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>5250.938472</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>4891.656505</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>5007.804521</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>5480.902817</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>4899.766521</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>5337.125867</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>4944.408426</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>4834.79714</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>5009.052167</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>5309.65149</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>5066.796285</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>4873.192551</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>5040.018696</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>5150.915715</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>4888.05621</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>5114.792318</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>4780.280193</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>4886.566848</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>4749.702534</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>5157.682633</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>5174.934835</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>4691.51829</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>4552.80818</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>4495.641913</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>4856.145415</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>4893.714047</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>4331.741438</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>4448.160455</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>4517.965829</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>4538.741213</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>4500.803841</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>4324.768578</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>4055.683368</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>4432.054262</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>4285.109574</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>4415.0272</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>4085.297745</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>4215.965954</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>4154.270252</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>4280.03669</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>4610.894467</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>4648.490502</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>3988.719049</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>3961.554212</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>4281.608819</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>4558.382933</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>4633.30178</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>4162.098346</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>4265.786792</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4352.895807</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>4275.920918</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>4434.557213</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>4338.554111</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>4119.40585</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>4451.120587</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>4200.493505</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>4337.878204</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>3929.100114</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4493.115087</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>4484.731054</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>4258.089465</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>4103.718765</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>4115.353162</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>4181.439999</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>4565.129328</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>4330.565589</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>4059.763057</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>4558.737767</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>4176.267977</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>4096.010576</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>4371.699785</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>4062.450867</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>4273.492413</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>4148.786355</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>4167.418836</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>4481.255818</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>4172.150682</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>4003.08696</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>3975.077711</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>4218.148994</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>4154.631794</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>4111.013141</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>4624.299726</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>4443.010076</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>4546.276345</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>4236.880581</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>4375.801171</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>4386.227355</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>4737.245905</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>4644.707188</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>4489.622779</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>4890.904707</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>4671.681983</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>4533.092348</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>4485.055058</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>4526.135261</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>4648.853874</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>4760.627418</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>4401.139095</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>4677.948348</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>4591.16347</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>4686.810724</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>4213.74211</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>4582.380771</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>4490.8349</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>4263.284939</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>4764.523767</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>4391.123777</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>4368.913278</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>5009.249608</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>4068.308834</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>4561.057646</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>4387.987621</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>4397.385311</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>4680.826493</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>4305.112131</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>4184.844538</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>4157.340743</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>4442.603992</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>4216.168734</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>4194.324406</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>4287.460691</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>4777.000561</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>4472.340793</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>4179.911227</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>4249.844913</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>4711.526253</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>4626.852177</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>4769.590557</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>4430.781989</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>4590.184953</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>5125.92247</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>5124.368831</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>4842.222634</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>4777.267647</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>5631.559349</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>5084.245581</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>5111.080225</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>4958.788185</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>5180.907791</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>5094.381406</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>5457.640651</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>5427.044268</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>5055.403492</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>5279.753655</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>5461.788222</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>5175.609653</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>5611.018016</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>5079.276068</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>5455.98922</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>4976.104282</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>5484.756665</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>5481.877116</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>5426.475355</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>5044.474322</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>5737.929628</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>5222.558176</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>4990.471952</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>4953.549037</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>4983.979267</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>4583.777471</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>5204.431621</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>5069.871855</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>4826.028707</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>4805.363863</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>4632.435571</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>4769.679518</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>4789.443293</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>4755.007112</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>4783.904964</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>4937.403536</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>5253.718994</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>4884.576982</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>5019.463765</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>4706.273947</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>5332.060382</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>5030.691297</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>5112.1468</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>4875.694772</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>5248.113409</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>5086.208795</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>5282.747824</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>5173.361973</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>5014.006615</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>5195.779995</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>5434.76071</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>5433.91958</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>5260.197291</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>5328.219881</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>5094.911459</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>5002.763579</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>5476.277566</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>5201.507992</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>5266.501524</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>5272.554592</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>5390.557961</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>5309.28701</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>4873.857057</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>4970.747932</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>5115.93391</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>4909.78721</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>4879.071661</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>5153.272976</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>4630.502703</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>4964.98966</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>5066.702585</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>5127.472309</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>4458.824462</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>4590.377871</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>4655.353191</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>4559.507878</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>4637.455515</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>4537.392532</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>4461.758059</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>4097.680493</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>4498.151774</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>4326.53963</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>4115.003331</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>4496.884322</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>4551.179152</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>4155.173748</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>4169.900296</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>4338.832079</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>4346.410253</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>4112.245025</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>4549.999198</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>4230.177522</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>4402.135997</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>4349.644188</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>4295.805662</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>4430.209665</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>4566.412129</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>4244.616116</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>3905.929174</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>4582.672561</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>4262.263925</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>4334.890462</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>4414.284739</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>4896.367426</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>4699.247173</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>4504.427376</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>4650.304852</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>4836.159596</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>4441.153183</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>4784.310145</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>4514.240733</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>4544.847985</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>4517.362619</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>4613.587869</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>4427.385167</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>4683.495642</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>4707.145136</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>4656.313917</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>4626.560351</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>4811.774598</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>4476.795116</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>4678.604022</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>4590.655923</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>4539.606999</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>4636.28717</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>4921.638719</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>4941.242705</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>4490.499137</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>4595.083651</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>5081.627182</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>4815.659692</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>4314.480571</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>4282.298027</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>4882.682757</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>4690.307209</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>4363.440944</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>4585.492889</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>4693.20014</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>4480.950092</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>4735.767752</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>4779.365789</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>4615.710051</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>4677.751227</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>5429.469368</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>4736.669293</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>4593.964613</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>4667.203714</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>4787.362963</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>4866.105574</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>4563.746502</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>4761.945689</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>4485.172542</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>4962.909656</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>4397.432157</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>4555.839117</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>4431.613694</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>4935.267106</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>4548.303667</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>5172.815364</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>4467.80085</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>4958.045243</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>4638.417056</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>4670.782509</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>5083.341634</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>4732.646409</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>4951.097535</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>4724.135475</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>4882.73944</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>5117.617451</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>4865.037729</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>4957.136546</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>5074.466048</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>4794.746347</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>4879.31745</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>4681.566807</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>4710.219391</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>4843.515904</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>4730.10947</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>4775.763246</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>4876.594939</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>4913.406524</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>4950.808774</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>4713.211334</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>4833.581058</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>4865.843175</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>5047.341085</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>4721.623703</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>4317.134138</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>4666.656877</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>4474.24357</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>4781.678061</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>4482.172672</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>4469.866693</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>4559.7262</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>4785.731213</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>4425.490052</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>4384.921031</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>4274.512621</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>4807.663157</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>4300.317269</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>4185.387987</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>4240.479873</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>4513.373461</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>4440.868564</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>4263.901163</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>4229.404059</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>4875.99101</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>4535.674759</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>4586.828992</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>4333.439252</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>4436.302458</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>4957.430811</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>4874.508172</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>4863.956576</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>4598.487688</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>5163.251772</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>4878.128325</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>5567.638781</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>5462.063021</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>5199.827542</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>5381.327438</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>5789.804307</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>5483.930013</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>5267.178667</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>5572.574329</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>6158.650857</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>5451.188268</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>5640.051588</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>6128.381102</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>6267.643949</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>6139.178939</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>5878.867476</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>6661.832412</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>6599.888759</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="0"/>
+        <c:smooth val="0"/>
+        <c:axId val="658126474"/>
+        <c:axId val="681581713"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="658126474"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="681581713"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="681581713"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="90200"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="658126474"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="1000"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="0" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr lang="en-US"/>
+      </a:pPr>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="10028">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst/>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="90200"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>31750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>279400</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3365500" y="31750"/>
+        <a:ext cx="7181850" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>82550</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3371850" y="2844800"/>
+        <a:ext cx="7181850" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>50800</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>393700</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3403600" y="5632450"/>
+        <a:ext cx="7258050" cy="2743200"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>31750</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>17145</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="3384550" y="8426450"/>
+        <a:ext cx="7239000" cy="4849495"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -8455,5 +17823,6 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>